--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -942,12 +942,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100933</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>594547.8917199697</v>
+        <v>594548</v>
       </c>
       <c r="R4" t="n">
-        <v>6607793.398050198</v>
+        <v>6607793</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,19 +1008,9 @@
           <t>1990-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1990-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>100933</v>
+        <v>100936</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>100936</v>
+        <v>100965</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>100965</v>
+        <v>100977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>100977</v>
+        <v>100978</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>100978</v>
+        <v>100983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>100983</v>
+        <v>100987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>100987</v>
+        <v>100989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -942,7 +942,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>100989</v>
+        <v>100999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -675,45 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6306116</v>
+        <v>3386494</v>
       </c>
       <c r="B2" t="n">
-        <v>98538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224913</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -725,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594390.860177516</v>
+        <v>594391</v>
       </c>
       <c r="R2" t="n">
-        <v>6607642.560869367</v>
+        <v>6607643</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-05-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-05-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>20 plantor med 30(14x1 + 4x2+3+5) blommor, varav 9 i knopp inom ca 6x1 meter. Dessutom två avbetade stjälkar. Obetad, igenväxande åkerholme med enar och granar. Fårbete för två år sedan. Fårbete utanför holmen 18/5. Granar borde tas bort och enar gallras.</t>
+          <t>I kant av fd åker, nu betesmark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,60 +787,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6306520</v>
+        <v>4709808</v>
       </c>
       <c r="B3" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224913</v>
+        <v>222295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kisslinge backe, östra sidan, Vstm</t>
+          <t>Kisslinge backe, sydvästra sidan, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>594550.9849367019</v>
+        <v>594391</v>
       </c>
       <c r="R3" t="n">
-        <v>6607791.450166089</v>
+        <v>6607643</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,27 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-05-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-05-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 knopp. Åsa Lindén visade 2/5. Hon såg backsippor för ca 5 år sedan. 2/5 sågs inga plantor. Betades av hästar till 1996-97, därefter obetat. Öppning i skogen, omgiven av stora granar, mycket fjolårsgräs, mossa i bottenskiktet gör lokalen starkt hotad.</t>
+          <t>2011-05-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +876,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Igenväxande före detta betesmark.</t>
+          <t>Obetad, igenväxande åkerholme</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,7 +897,7 @@
         <v>6283130</v>
       </c>
       <c r="B4" t="n">
-        <v>100999</v>
+        <v>101347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1046,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6328769</v>
+        <v>6306116</v>
       </c>
       <c r="B5" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,7 +1027,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1092,14 +1042,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kisslinge backe, östra sidan, Vstm</t>
+          <t>Kisslinge backe, sydvästra sidan, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>594542.7193466426</v>
+        <v>594391</v>
       </c>
       <c r="R5" t="n">
-        <v>6607797.319395682</v>
+        <v>6607643</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1126,27 +1076,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-05-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-05-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2 plantor nära varandra (eller möjligen 1 planta) med 2 (1+1) blommor. I glänta, intill stor gran, som är ett hot mot backsipporna. Ca 8 meter mot skogen från planta vid stig mellan granarna. Drog bort stor tallgren som låg alldeles intill backsipporna.</t>
+          <t>20 plantor med 30(14x1 + 4x2+3+5) blommor, varav 9 i knopp inom ca 6x1 meter. Dessutom två avbetade stjälkar. Obetad, igenväxande åkerholme med enar och granar. Fårbete för två år sedan. Fårbete utanför holmen 18/5. Granar borde tas bort och enar gallras.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,7 +1100,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Igenväxande före detta betesmark</t>
+          <t>Obetad, igenväxande åkerholme</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,55 +1118,55 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4709808</v>
+        <v>6306520</v>
       </c>
       <c r="B6" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>224913</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kisslinge backe, sydvästra sidan, Vstm</t>
+          <t>Kisslinge backe, östra sidan, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>594390.860177516</v>
+        <v>594551</v>
       </c>
       <c r="R6" t="n">
-        <v>6607642.560869367</v>
+        <v>6607791</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1253,22 +1193,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-05-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-05-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-05-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 knopp. Åsa Lindén visade 2/5. Hon såg backsippor för ca 5 år sedan. 2/5 sågs inga plantor. Betades av hästar till 1996-97, därefter obetat. Öppning i skogen, omgiven av stora granar, mycket fjolårsgräs, mossa i bottenskiktet gör lokalen starkt hotad.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,7 +1217,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Obetad, igenväxande åkerholme</t>
+          <t>Igenväxande före detta betesmark.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1300,40 +1235,40 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3386494</v>
+        <v>6328769</v>
       </c>
       <c r="B7" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221141</v>
+        <v>224913</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Primula veris</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -1341,14 +1276,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kisslinge backe, sydvästra sidan, Vstm</t>
+          <t>Kisslinge backe, östra sidan, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>594390.860177516</v>
+        <v>594543</v>
       </c>
       <c r="R7" t="n">
-        <v>6607642.560869367</v>
+        <v>6607797</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1375,27 +1310,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-05-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-05-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-05-06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>I kant av fd åker, nu betesmark.</t>
+          <t>2 plantor nära varandra (eller möjligen 1 planta) med 2 (1+1) blommor. I glänta, intill stor gran, som är ett hot mot backsipporna. Ca 8 meter mot skogen från planta vid stig mellan granarna. Drog bort stor tallgren som låg alldeles intill backsipporna.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,7 +1334,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Obetad, igenväxande åkerholme</t>
+          <t>Igenväxande före detta betesmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 64735-2023 artfynd.xlsx
+++ b/artfynd/A 64735-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3386494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4709808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
           <t>Kärlväxtinventering U-län, Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6283130</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6306116</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6306520</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,8 +1379,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6328769</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>